--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108198606</v>
+        <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96669</v>
+        <v>96792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2086</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kalkfickmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fissidens gracilifolius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Brugg.-Nann. &amp; Nyholm</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Annedal, 290 m S om, Dls</t>
+          <t>Annedal, ca 310 m S-SSV om, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>336817</v>
+        <v>336798</v>
       </c>
       <c r="R2" t="n">
-        <v>6521226</v>
+        <v>6521210</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>V-vänd bergbrant i skog, rikt.</t>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -781,16 +786,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108198606</t>
+          <t>https://artportalen.se/Sighting/137080323</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108198596</v>
+        <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>95944</v>
+        <v>96792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2362</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Annedal, 290 m S om, Dls</t>
+          <t>Annedal, ca 275 m S-SSV om, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>336817</v>
+        <v>336820</v>
       </c>
       <c r="R3" t="n">
-        <v>6521226</v>
+        <v>6521240</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +876,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>V-vänd bergbrant i skog, rikt.</t>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>På grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -888,51 +898,51 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108198596</t>
+          <t>https://artportalen.se/Sighting/137080331</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115786329</v>
+        <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>95944</v>
+        <v>97822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2362</v>
+        <v>232</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Vedsäckmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Calypogeia suecica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Annedal, ca 400 m S-SSV om, Bäckefors, Dls</t>
+          <t>Annedal, ca 275 m S-SSV om, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>336795</v>
+        <v>336820</v>
       </c>
       <c r="R4" t="n">
-        <v>6521113</v>
+        <v>6521240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,12 +988,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Blandskog gran och ädellöv, mycket hassel.</t>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På V-vänd bergvägg. Rikt.</t>
+          <t>På grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1000,51 +1010,51 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115786329</t>
+          <t>https://artportalen.se/Sighting/137080330</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115786326</v>
+        <v>108198606</v>
       </c>
       <c r="B5" t="n">
-        <v>97812</v>
+        <v>96669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2605</v>
+        <v>2086</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stenporella</t>
+          <t>Kalkfickmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porella cordaeana</t>
+          <t>Fissidens gracilifolius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Huebener) Moore</t>
+          <t>Brugg.-Nann. &amp; Nyholm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Annedal, ca 400 m S-SSV om, Bäckefors, Dls</t>
+          <t>Annedal, 290 m S om, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>336795</v>
+        <v>336817</v>
       </c>
       <c r="R5" t="n">
-        <v>6521113</v>
+        <v>6521226</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,12 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,12 +1100,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Blandskog gran och ädellöv, mycket hassel.</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>På V-vänd bergvägg. Rikt.</t>
+          <t>V-vänd bergbrant i skog, rikt.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1112,16 +1117,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115786326</t>
+          <t>https://artportalen.se/Sighting/108198606</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108198602</v>
+        <v>108198596</v>
       </c>
       <c r="B6" t="n">
-        <v>96439</v>
+        <v>95944</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2666</v>
+        <v>2362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1219,16 +1224,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108198602</t>
+          <t>https://artportalen.se/Sighting/108198596</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108198608</v>
+        <v>115786329</v>
       </c>
       <c r="B7" t="n">
-        <v>96439</v>
+        <v>95944</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,34 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2666</v>
+        <v>2362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Annedal, 275 m S om, Dls</t>
+          <t>Annedal, ca 400 m S-SSV om, Bäckefors, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>336844</v>
+        <v>336795</v>
       </c>
       <c r="R7" t="n">
-        <v>6521228</v>
+        <v>6521113</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,12 +1295,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,7 +1314,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>V-vänd bergbrant i skog, rikt.</t>
+          <t>Blandskog gran och ädellöv, mycket hassel.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>På V-vänd bergvägg. Rikt.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1326,16 +1336,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108198608</t>
+          <t>https://artportalen.se/Sighting/115786329</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115786331</v>
+        <v>115786326</v>
       </c>
       <c r="B8" t="n">
-        <v>96439</v>
+        <v>97812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2666</v>
+        <v>2605</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Stenporella</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Porella cordaeana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Huebener) Moore</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1438,16 +1448,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115786331</t>
+          <t>https://artportalen.se/Sighting/115786326</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108198614</v>
+        <v>108198602</v>
       </c>
       <c r="B9" t="n">
-        <v>96437</v>
+        <v>96439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,16 +1465,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1475,14 +1485,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Annedal, 275 m S om, Dls</t>
+          <t>Annedal, 290 m S om, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>336844</v>
+        <v>336817</v>
       </c>
       <c r="R9" t="n">
-        <v>6521228</v>
+        <v>6521226</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,16 +1555,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108198614</t>
+          <t>https://artportalen.se/Sighting/108198602</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115786332</v>
+        <v>108198608</v>
       </c>
       <c r="B10" t="n">
-        <v>96437</v>
+        <v>96439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,16 +1572,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1582,14 +1592,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Annedal, ca 400 m S-SSV om, Bäckefors, Dls</t>
+          <t>Annedal, 275 m S om, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>336795</v>
+        <v>336844</v>
       </c>
       <c r="R10" t="n">
-        <v>6521113</v>
+        <v>6521228</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,12 +1626,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1635,12 +1645,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Blandskog gran och ädellöv, mycket hassel.</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>På V-vänd bergvägg. Rikt.</t>
+          <t>V-vänd bergbrant i skog, rikt.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1657,16 +1662,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115786332</t>
+          <t>https://artportalen.se/Sighting/108198608</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115786328</v>
+        <v>115786331</v>
       </c>
       <c r="B11" t="n">
-        <v>96186</v>
+        <v>96439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2676</v>
+        <v>2666</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1769,16 +1774,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115786328</t>
+          <t>https://artportalen.se/Sighting/115786331</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108198605</v>
+        <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96231</v>
+        <v>96677</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,34 +1791,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2779</v>
+        <v>2666</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Annedal, 290 m S om, Dls</t>
+          <t>Annedal, ca 360 m S-SSV om, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>336817</v>
+        <v>336804</v>
       </c>
       <c r="R12" t="n">
-        <v>6521226</v>
+        <v>6521158</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,12 +1845,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,7 +1864,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>V-vänd bergbrant i skog, rikt.</t>
+          <t>Hög, västvänd bergvägg i rik barrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1876,16 +1881,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108198605</t>
+          <t>https://artportalen.se/Sighting/137080286</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108198595</v>
+        <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96338</v>
+        <v>96677</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,34 +1898,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>2666</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Annedal, 350 m S om, Dls</t>
+          <t>Annedal, ca 340 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>336807</v>
+        <v>336738</v>
       </c>
       <c r="R13" t="n">
-        <v>6521171</v>
+        <v>6521201</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,12 +1952,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,7 +1971,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Sumpig granskog.</t>
+          <t>Östvänd lodyta i rik barrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1983,16 +1988,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108198595</t>
+          <t>https://artportalen.se/Sighting/137080302</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115786347</v>
+        <v>108198614</v>
       </c>
       <c r="B14" t="n">
-        <v>96338</v>
+        <v>96437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,34 +2005,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Annedal, ca 325 m SSV om, Bäckefors, Dls</t>
+          <t>Annedal, 275 m S om, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>336787</v>
+        <v>336844</v>
       </c>
       <c r="R14" t="n">
-        <v>6521191</v>
+        <v>6521228</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,12 +2059,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,12 +2078,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Frisk-fuktig granskog.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>På marken.</t>
+          <t>V-vänd bergbrant i skog, rikt.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2095,16 +2095,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115786347</t>
+          <t>https://artportalen.se/Sighting/108198614</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108198592</v>
+        <v>115786332</v>
       </c>
       <c r="B15" t="n">
-        <v>96350</v>
+        <v>96437</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,39 +2112,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2813</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Annedal, 350 m S om, Dls</t>
+          <t>Annedal, ca 400 m S-SSV om, Bäckefors, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>336807</v>
+        <v>336795</v>
       </c>
       <c r="R15" t="n">
-        <v>6521171</v>
+        <v>6521113</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,12 +2166,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2190,7 +2185,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Sumpig granskog.</t>
+          <t>Blandskog gran och ädellöv, mycket hassel.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>På V-vänd bergvägg. Rikt.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2207,16 +2207,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108198592</t>
+          <t>https://artportalen.se/Sighting/115786332</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115786339</v>
+        <v>115786328</v>
       </c>
       <c r="B16" t="n">
-        <v>96350</v>
+        <v>96186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,34 +2224,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2813</v>
+        <v>2676</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Annedal, ca 325 m SSV om, Bäckefors, Dls</t>
+          <t>Annedal, ca 400 m S-SSV om, Bäckefors, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>336787</v>
+        <v>336795</v>
       </c>
       <c r="R16" t="n">
-        <v>6521191</v>
+        <v>6521113</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Frisk-fuktig granskog.</t>
+          <t>Blandskog gran och ädellöv, mycket hassel.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>På marken.</t>
+          <t>På V-vänd bergvägg. Rikt.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2319,16 +2319,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115786339</t>
+          <t>https://artportalen.se/Sighting/115786328</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>108198586</v>
+        <v>108198605</v>
       </c>
       <c r="B17" t="n">
-        <v>96458</v>
+        <v>96231</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,34 +2336,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Annedal, 350 m S om, Dls</t>
+          <t>Annedal, 290 m S om, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>336807</v>
+        <v>336817</v>
       </c>
       <c r="R17" t="n">
-        <v>6521171</v>
+        <v>6521226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,12 +2409,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Sumpig granskog.</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Granlåga.</t>
+          <t>V-vänd bergbrant i skog, rikt.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2431,16 +2426,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108198586</t>
+          <t>https://artportalen.se/Sighting/108198605</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115786336</v>
+        <v>108198595</v>
       </c>
       <c r="B18" t="n">
-        <v>96458</v>
+        <v>96338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,34 +2443,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Annedal, ca 315 m S-SSV om, Bäckefors, Dls</t>
+          <t>Annedal, 350 m S om, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>336812</v>
+        <v>336807</v>
       </c>
       <c r="R18" t="n">
-        <v>6521203</v>
+        <v>6521171</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,12 +2497,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2521,12 +2516,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Frisk-fuktig granskog.</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>På marken.</t>
+          <t>Sumpig granskog.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2543,51 +2533,51 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115786336</t>
+          <t>https://artportalen.se/Sighting/108198595</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133235936</v>
+        <v>115786347</v>
       </c>
       <c r="B19" t="n">
-        <v>101974</v>
+        <v>96338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220075</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stora Ödegården, 360 m NO om, Dls</t>
+          <t>Annedal, ca 325 m SSV om, Bäckefors, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>336791</v>
+        <v>336787</v>
       </c>
       <c r="R19" t="n">
-        <v>6521155</v>
+        <v>6521191</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,12 +2604,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2630,6 +2620,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig granskog.</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>På marken.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2639,13 +2639,3141 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Niklas Lönnell</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/115786347</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137080294</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96576</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Annedal, ca 340 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>336772</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6521187</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Rik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080294</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137080325</v>
+      </c>
+      <c r="B21" t="n">
+        <v>96576</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Annedal, ca 310 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>336798</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6521210</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080325</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137080332</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96576</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Annedal, ca 270 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>336820</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6521249</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080332</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137080335</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96576</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Annedal, ca 275 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>336789</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6521251</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080335</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137080340</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96576</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Annedal, ca 260 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>336790</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6521266</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080340</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137080293</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96573</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Annedal, ca 340 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>336772</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6521187</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Rik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080293</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137080307</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96573</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Annedal, ca 325 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>336747</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6521211</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080307</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137080313</v>
+      </c>
+      <c r="B27" t="n">
+        <v>96573</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Annedal, ca 310 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>336742</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6521230</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080313</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137080317</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96573</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Annedal, ca 310 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>336757</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6521224</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080317</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137080338</v>
+      </c>
+      <c r="B29" t="n">
+        <v>96573</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Annedal, ca 260 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>336790</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6521266</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080338</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>108198592</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Annedal, 350 m S om, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>336807</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6521171</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Sumpig granskog.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108198592</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>115786339</v>
+      </c>
+      <c r="B31" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Annedal, ca 325 m SSV om, Bäckefors, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>336787</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6521191</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig granskog.</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>På marken.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115786339</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137080290</v>
+      </c>
+      <c r="B32" t="n">
+        <v>96588</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Annedal, ca 380 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>336790</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6521138</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Rik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080290</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137080292</v>
+      </c>
+      <c r="B33" t="n">
+        <v>96588</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Annedal, ca 345 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>336781</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6521180</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Rik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080292</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137080324</v>
+      </c>
+      <c r="B34" t="n">
+        <v>96588</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Annedal, ca 310 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>336798</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6521210</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080324</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137080326</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96588</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Annedal, ca 300 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>336823</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6521216</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080326</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137080333</v>
+      </c>
+      <c r="B36" t="n">
+        <v>96588</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Annedal, ca 275 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>336813</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6521242</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080333</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137080334</v>
+      </c>
+      <c r="B37" t="n">
+        <v>96588</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Annedal, ca 280 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>336798</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6521243</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080334</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>108198586</v>
+      </c>
+      <c r="B38" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Annedal, 350 m S om, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>336807</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6521171</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Sumpig granskog.</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Granlåga.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108198586</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>115786336</v>
+      </c>
+      <c r="B39" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Annedal, ca 315 m S-SSV om, Bäckefors, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>336812</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6521203</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Frisk-fuktig granskog.</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>På marken.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115786336</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137080322</v>
+      </c>
+      <c r="B40" t="n">
+        <v>96696</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Annedal, ca 310 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>336798</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6521210</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>På grov, murken granlåga.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080322</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137080329</v>
+      </c>
+      <c r="B41" t="n">
+        <v>96696</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Annedal, ca 275 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>336820</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6521240</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>På grov, murken granlåga.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080329</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133235936</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101974</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stora Ödegården, 360 m NO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>336791</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6521155</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Leif Appelgren, Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133235936</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137080314</v>
+      </c>
+      <c r="B43" t="n">
+        <v>108386</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Annedal, ca 310 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>336742</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6521230</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080314</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137080318</v>
+      </c>
+      <c r="B44" t="n">
+        <v>108386</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Annedal, ca 310 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>336757</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6521224</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080318</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137080284</v>
+      </c>
+      <c r="B45" t="n">
+        <v>104371</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221987</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skogsbingel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Mercurialis perennis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Annedal, ca 310 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>336790</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6521213</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080284</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137080285</v>
+      </c>
+      <c r="B46" t="n">
+        <v>104371</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221987</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skogsbingel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Mercurialis perennis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Annedal, ca 325 m S-SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>336789</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6521197</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080285</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137080310</v>
+      </c>
+      <c r="B47" t="n">
+        <v>104371</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221987</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skogsbingel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Mercurialis perennis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Annedal, ca 325 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>336747</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6521211</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Storväxt, gles granskog med hassel, troligen planterad på gammal åkermark. Rik, fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080310</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137080295</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Annedal, ca 350 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>336737</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6521193</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Östvänd lodyta i rik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080295</t>
         </is>
       </c>
     </row>
@@ -2669,6 +5797,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97822</v>
+        <v>97823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96677</v>
+        <v>96678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96677</v>
+        <v>96678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96588</v>
+        <v>96589</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96588</v>
+        <v>96589</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96588</v>
+        <v>96589</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96588</v>
+        <v>96589</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96588</v>
+        <v>96589</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96588</v>
+        <v>96589</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104371</v>
+        <v>104372</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104371</v>
+        <v>104372</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104371</v>
+        <v>104372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97823</v>
+        <v>97829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96678</v>
+        <v>96684</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96678</v>
+        <v>96684</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96589</v>
+        <v>96595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96589</v>
+        <v>96595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96589</v>
+        <v>96595</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96589</v>
+        <v>96595</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96589</v>
+        <v>96595</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96589</v>
+        <v>96595</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104372</v>
+        <v>104378</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104372</v>
+        <v>104378</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104372</v>
+        <v>104378</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97829</v>
+        <v>97833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96684</v>
+        <v>96688</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96684</v>
+        <v>96688</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96595</v>
+        <v>96599</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96595</v>
+        <v>96599</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96595</v>
+        <v>96599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96595</v>
+        <v>96599</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96595</v>
+        <v>96599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96595</v>
+        <v>96599</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104378</v>
+        <v>104382</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104378</v>
+        <v>104382</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104378</v>
+        <v>104382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97833</v>
+        <v>97835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96688</v>
+        <v>96690</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96688</v>
+        <v>96690</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104382</v>
+        <v>104384</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104382</v>
+        <v>104384</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104382</v>
+        <v>104384</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97835</v>
+        <v>97837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96690</v>
+        <v>96692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96690</v>
+        <v>96692</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104384</v>
+        <v>104386</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104384</v>
+        <v>104386</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104384</v>
+        <v>104386</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97837</v>
+        <v>97850</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96692</v>
+        <v>96705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96692</v>
+        <v>96705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96603</v>
+        <v>96616</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96603</v>
+        <v>96616</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96603</v>
+        <v>96616</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96603</v>
+        <v>96616</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96603</v>
+        <v>96616</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96603</v>
+        <v>96616</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104386</v>
+        <v>104399</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104386</v>
+        <v>104399</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104386</v>
+        <v>104399</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97850</v>
+        <v>97852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96705</v>
+        <v>96707</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96705</v>
+        <v>96707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96616</v>
+        <v>96618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96616</v>
+        <v>96618</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96616</v>
+        <v>96618</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96616</v>
+        <v>96618</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96616</v>
+        <v>96618</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96616</v>
+        <v>96618</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104399</v>
+        <v>104401</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104399</v>
+        <v>104401</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104399</v>
+        <v>104401</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97852</v>
+        <v>97855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96707</v>
+        <v>96710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96707</v>
+        <v>96710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96618</v>
+        <v>96621</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96618</v>
+        <v>96621</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96618</v>
+        <v>96621</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96618</v>
+        <v>96621</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96618</v>
+        <v>96621</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96618</v>
+        <v>96621</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104401</v>
+        <v>104404</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104401</v>
+        <v>104404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104401</v>
+        <v>104404</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97855</v>
+        <v>97865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96710</v>
+        <v>96720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96710</v>
+        <v>96720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96621</v>
+        <v>96631</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96621</v>
+        <v>96631</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96621</v>
+        <v>96631</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96621</v>
+        <v>96631</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96621</v>
+        <v>96631</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96621</v>
+        <v>96631</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104404</v>
+        <v>104419</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104404</v>
+        <v>104419</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104404</v>
+        <v>104419</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97865</v>
+        <v>97866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96631</v>
+        <v>96632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96631</v>
+        <v>96632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96631</v>
+        <v>96632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96631</v>
+        <v>96632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96631</v>
+        <v>96632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96631</v>
+        <v>96632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104419</v>
+        <v>104420</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104419</v>
+        <v>104420</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104419</v>
+        <v>104420</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97866</v>
+        <v>97871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96721</v>
+        <v>96726</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96721</v>
+        <v>96726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96632</v>
+        <v>96637</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96632</v>
+        <v>96637</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96632</v>
+        <v>96637</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96632</v>
+        <v>96637</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96632</v>
+        <v>96637</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96632</v>
+        <v>96637</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104420</v>
+        <v>104425</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104420</v>
+        <v>104425</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104420</v>
+        <v>104425</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97871</v>
+        <v>97873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96726</v>
+        <v>96728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96726</v>
+        <v>96728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96637</v>
+        <v>96639</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96637</v>
+        <v>96639</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96637</v>
+        <v>96639</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96637</v>
+        <v>96639</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96637</v>
+        <v>96639</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96637</v>
+        <v>96639</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104425</v>
+        <v>104428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104425</v>
+        <v>104428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104425</v>
+        <v>104428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97873</v>
+        <v>97879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96728</v>
+        <v>96734</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96728</v>
+        <v>96734</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96639</v>
+        <v>96645</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96639</v>
+        <v>96645</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96639</v>
+        <v>96645</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96639</v>
+        <v>96645</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96639</v>
+        <v>96645</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96639</v>
+        <v>96645</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104428</v>
+        <v>104434</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104428</v>
+        <v>104434</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104428</v>
+        <v>104434</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104434</v>
+        <v>104435</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104434</v>
+        <v>104435</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104434</v>
+        <v>104435</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97879</v>
+        <v>97891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96734</v>
+        <v>96746</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96734</v>
+        <v>96746</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96645</v>
+        <v>96657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96645</v>
+        <v>96657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96645</v>
+        <v>96657</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96645</v>
+        <v>96657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96645</v>
+        <v>96657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96645</v>
+        <v>96657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104435</v>
+        <v>104447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104435</v>
+        <v>104447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104435</v>
+        <v>104447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97891</v>
+        <v>97892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96746</v>
+        <v>96747</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96746</v>
+        <v>96747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96657</v>
+        <v>96658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96657</v>
+        <v>96658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96657</v>
+        <v>96658</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96657</v>
+        <v>96658</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96657</v>
+        <v>96658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96657</v>
+        <v>96658</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104447</v>
+        <v>104448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104447</v>
+        <v>104448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104447</v>
+        <v>104448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97892</v>
+        <v>97895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96747</v>
+        <v>96750</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96747</v>
+        <v>96750</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96658</v>
+        <v>96661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96658</v>
+        <v>96661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96658</v>
+        <v>96661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96658</v>
+        <v>96661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96658</v>
+        <v>96661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96658</v>
+        <v>96661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104448</v>
+        <v>104451</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104448</v>
+        <v>104451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104448</v>
+        <v>104451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 39053-2026 artfynd.xlsx
+++ b/artfynd/A 39053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137080323</v>
       </c>
       <c r="B2" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137080331</v>
       </c>
       <c r="B3" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137080330</v>
       </c>
       <c r="B4" t="n">
-        <v>97895</v>
+        <v>97899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>137080286</v>
       </c>
       <c r="B12" t="n">
-        <v>96750</v>
+        <v>96754</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>137080302</v>
       </c>
       <c r="B13" t="n">
-        <v>96750</v>
+        <v>96754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>137080294</v>
       </c>
       <c r="B20" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>137080325</v>
       </c>
       <c r="B21" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137080332</v>
       </c>
       <c r="B22" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>137080335</v>
       </c>
       <c r="B23" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>137080340</v>
       </c>
       <c r="B24" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137080293</v>
       </c>
       <c r="B25" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137080307</v>
       </c>
       <c r="B26" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>137080313</v>
       </c>
       <c r="B27" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>137080317</v>
       </c>
       <c r="B28" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137080338</v>
       </c>
       <c r="B29" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137080290</v>
       </c>
       <c r="B32" t="n">
-        <v>96661</v>
+        <v>96665</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137080292</v>
       </c>
       <c r="B33" t="n">
-        <v>96661</v>
+        <v>96665</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137080324</v>
       </c>
       <c r="B34" t="n">
-        <v>96661</v>
+        <v>96665</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>137080326</v>
       </c>
       <c r="B35" t="n">
-        <v>96661</v>
+        <v>96665</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>137080333</v>
       </c>
       <c r="B36" t="n">
-        <v>96661</v>
+        <v>96665</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>137080334</v>
       </c>
       <c r="B37" t="n">
-        <v>96661</v>
+        <v>96665</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>137080322</v>
       </c>
       <c r="B40" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>137080329</v>
       </c>
       <c r="B41" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>137080314</v>
       </c>
       <c r="B43" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>137080318</v>
       </c>
       <c r="B44" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>137080284</v>
       </c>
       <c r="B45" t="n">
-        <v>104451</v>
+        <v>104456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>137080285</v>
       </c>
       <c r="B46" t="n">
-        <v>104451</v>
+        <v>104456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137080310</v>
       </c>
       <c r="B47" t="n">
-        <v>104451</v>
+        <v>104456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>137080295</v>
       </c>
       <c r="B48" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
